--- a/Result/profitability/1737.xlsx
+++ b/Result/profitability/1737.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.09</v>
       </c>
       <c r="M2" t="n">
-        <v>0.40375</v>
+        <v>0.39625</v>
       </c>
       <c r="N2" t="n">
-        <v>39.83499999999999</v>
+        <v>39.62625000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0.34125</v>
+        <v>0.34375</v>
       </c>
       <c r="N3" t="n">
-        <v>39.5575</v>
+        <v>39.4325</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.14</v>
       </c>
       <c r="M4" t="n">
-        <v>0.27625</v>
+        <v>0.265</v>
       </c>
       <c r="N4" t="n">
-        <v>39.005</v>
+        <v>38.825</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.21</v>
       </c>
       <c r="M5" t="n">
-        <v>0.18875</v>
+        <v>0.18375</v>
       </c>
       <c r="N5" t="n">
-        <v>38.5025</v>
+        <v>37.83125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.19</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1575</v>
+        <v>0.1625</v>
       </c>
       <c r="N6" t="n">
-        <v>37.6825</v>
+        <v>37.4725</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.27</v>
       </c>
       <c r="M7" t="n">
-        <v>0.14625</v>
+        <v>0.10625</v>
       </c>
       <c r="N7" t="n">
-        <v>37.5125</v>
+        <v>37.33</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.07875</v>
       </c>
       <c r="N8" t="n">
-        <v>37.48375</v>
+        <v>37.19375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.0325</v>
       </c>
       <c r="N9" t="n">
-        <v>37.65750000000001</v>
+        <v>37.6575</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>769</v>
+      </c>
+      <c r="D75" t="n">
+        <v>476</v>
+      </c>
+      <c r="E75" t="n">
+        <v>293</v>
+      </c>
+      <c r="F75" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="G75" t="n">
+        <v>76</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.87%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>17</v>
+      </c>
+      <c r="J75" t="n">
+        <v>93</v>
+      </c>
+      <c r="K75" t="n">
+        <v>80</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.9475</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.06999999999999995</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1489361702127658</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.05742574257425748</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.03999999999999998</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.09090909090909083</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.370000000000005</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1235903337169161</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
